--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484125_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484125_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>11.1972</v>
+        <v>9.646100000000001</v>
       </c>
       <c r="E2" t="n">
-        <v>9.3786</v>
+        <v>8.585000000000001</v>
       </c>
       <c r="F2" t="n">
-        <v>1.8186</v>
+        <v>1.0611</v>
       </c>
       <c r="G2" t="n">
         <v>6.4524</v>
@@ -610,13 +610,13 @@
         <v>3.1741</v>
       </c>
       <c r="S2" t="n">
-        <v>2.1533</v>
+        <v>0.6022</v>
       </c>
       <c r="T2" t="n">
-        <v>0.805</v>
+        <v>0.0115</v>
       </c>
       <c r="U2" t="n">
-        <v>1.3483</v>
+        <v>0.5908</v>
       </c>
       <c r="V2" t="n">
         <v>1.4012</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>6.5407</v>
+        <v>5.7333</v>
       </c>
       <c r="E3" t="n">
-        <v>5.3649</v>
+        <v>4.3049</v>
       </c>
       <c r="F3" t="n">
-        <v>1.1758</v>
+        <v>1.4283</v>
       </c>
       <c r="G3" t="n">
         <v>2.5601</v>
@@ -688,13 +688,13 @@
         <v>4.1661</v>
       </c>
       <c r="S3" t="n">
-        <v>1.4098</v>
+        <v>0.6022999999999999</v>
       </c>
       <c r="T3" t="n">
-        <v>2.2278</v>
+        <v>1.1678</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.8179999999999999</v>
+        <v>-0.5655</v>
       </c>
       <c r="V3" t="n">
         <v>-0.6032</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>3.8544</v>
+        <v>4.9308</v>
       </c>
       <c r="E4" t="n">
-        <v>2.0614</v>
+        <v>3.0817</v>
       </c>
       <c r="F4" t="n">
-        <v>1.793</v>
+        <v>1.8491</v>
       </c>
       <c r="G4" t="n">
         <v>4.7571</v>
@@ -766,13 +766,13 @@
         <v>2.9758</v>
       </c>
       <c r="S4" t="n">
-        <v>-1.3626</v>
+        <v>-0.2862</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.6858</v>
+        <v>0.3345</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.6768</v>
+        <v>-0.6207</v>
       </c>
       <c r="V4" t="n">
         <v>-0.532</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.2362</v>
+        <v>1.3663</v>
       </c>
       <c r="E5" t="n">
-        <v>2.5594</v>
+        <v>2.6615</v>
       </c>
       <c r="F5" t="n">
-        <v>-1.3232</v>
+        <v>-1.2952</v>
       </c>
       <c r="G5" t="n">
         <v>1.0802</v>
@@ -844,13 +844,13 @@
         <v>2.579</v>
       </c>
       <c r="S5" t="n">
-        <v>0.0414</v>
+        <v>0.1715</v>
       </c>
       <c r="T5" t="n">
-        <v>0.4252</v>
+        <v>0.5272</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.3838</v>
+        <v>-0.3558</v>
       </c>
       <c r="V5" t="n">
         <v>-1.4724</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.094</v>
+        <v>-0.0098</v>
       </c>
       <c r="E6" t="n">
         <v>-0.9518</v>
       </c>
       <c r="F6" t="n">
-        <v>0.8578</v>
+        <v>0.9419</v>
       </c>
       <c r="G6" t="n">
         <v>-0.4335</v>
@@ -922,13 +922,13 @@
         <v>0.5952</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.2556</v>
+        <v>-0.1714</v>
       </c>
       <c r="T6" t="n">
         <v>-0.3117</v>
       </c>
       <c r="U6" t="n">
-        <v>0.0561</v>
+        <v>0.1403</v>
       </c>
       <c r="V6" t="n">
         <v>0</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.2462</v>
+        <v>-0.0858</v>
       </c>
       <c r="E7" t="n">
-        <v>-2.0386</v>
+        <v>-1.7099</v>
       </c>
       <c r="F7" t="n">
-        <v>1.7924</v>
+        <v>1.624</v>
       </c>
       <c r="G7" t="n">
         <v>0.9397</v>
@@ -1000,13 +1000,13 @@
         <v>2.3806</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.9795</v>
+        <v>-0.819</v>
       </c>
       <c r="T7" t="n">
-        <v>-1.2979</v>
+        <v>-0.9691</v>
       </c>
       <c r="U7" t="n">
-        <v>0.3184</v>
+        <v>0.1501</v>
       </c>
       <c r="V7" t="n">
         <v>-0.6032</v>
@@ -1033,10 +1033,10 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.6983</v>
+        <v>-0.3298</v>
       </c>
       <c r="E8" t="n">
-        <v>1.0194</v>
+        <v>1.3879</v>
       </c>
       <c r="F8" t="n">
         <v>-1.7177</v>
@@ -1078,10 +1078,10 @@
         <v>1.7855</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.8445</v>
+        <v>-0.4761</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.0679</v>
+        <v>0.3005</v>
       </c>
       <c r="U8" t="n">
         <v>-0.7766</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>P. FEIXA MORANCHO</t>
+          <t>F. LOPEZ BARCELO</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.9463</v>
+        <v>-1.665</v>
       </c>
       <c r="E9" t="n">
-        <v>0.7183</v>
+        <v>-1.0434</v>
       </c>
       <c r="F9" t="n">
-        <v>-2.6646</v>
+        <v>-0.6216</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.2323</v>
+        <v>-2.4863</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.4486</v>
+        <v>-0.5442</v>
       </c>
       <c r="I9" t="n">
-        <v>0.2164</v>
+        <v>-1.9422</v>
       </c>
       <c r="J9" t="n">
-        <v>0.1005</v>
+        <v>-1.6273</v>
       </c>
       <c r="K9" t="n">
-        <v>0.0202</v>
+        <v>-0.3523</v>
       </c>
       <c r="L9" t="n">
-        <v>0.0803</v>
+        <v>-1.275</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.3328</v>
+        <v>-0.859</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.4688</v>
+        <v>-0.1918</v>
       </c>
       <c r="O9" t="n">
-        <v>0.136</v>
+        <v>-0.6672</v>
       </c>
       <c r="P9" t="n">
-        <v>0.1984</v>
+        <v>1.7855</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>0.1984</v>
+        <v>1.7855</v>
       </c>
       <c r="S9" t="n">
-        <v>0.5004999999999999</v>
+        <v>0.2423</v>
       </c>
       <c r="T9" t="n">
-        <v>0.6178</v>
+        <v>0.5839</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.1173</v>
+        <v>-0.3415</v>
       </c>
       <c r="V9" t="n">
-        <v>-2.4129</v>
+        <v>-1.2065</v>
       </c>
       <c r="W9" t="n">
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>-2.4129</v>
+        <v>-1.2065</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>F. LOPEZ BARCELO</t>
+          <t>P. FEIXA MORANCHO</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.7694</v>
+        <v>-2.3264</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.0637</v>
+        <v>0.3102</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.7057</v>
+        <v>-2.6366</v>
       </c>
       <c r="G10" t="n">
-        <v>-2.4863</v>
+        <v>-0.2323</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.5442</v>
+        <v>-0.4486</v>
       </c>
       <c r="I10" t="n">
-        <v>-1.9422</v>
+        <v>0.2164</v>
       </c>
       <c r="J10" t="n">
-        <v>-1.6273</v>
+        <v>0.1005</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.3523</v>
+        <v>0.0202</v>
       </c>
       <c r="L10" t="n">
-        <v>-1.275</v>
+        <v>0.0803</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.859</v>
+        <v>-0.3328</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.1918</v>
+        <v>-0.4688</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.6672</v>
+        <v>0.136</v>
       </c>
       <c r="P10" t="n">
-        <v>1.7855</v>
+        <v>0.1984</v>
       </c>
       <c r="Q10" t="n">
         <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>1.7855</v>
+        <v>0.1984</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.8621</v>
+        <v>0.1205</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.4364</v>
+        <v>0.2097</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.4257</v>
+        <v>-0.0893</v>
       </c>
       <c r="V10" t="n">
-        <v>-1.2065</v>
+        <v>-2.4129</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>-1.2065</v>
+        <v>-2.4129</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>J. HAGENAERS COS</t>
+          <t>A. PILAN PERET</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,73 +1267,73 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-3.1875</v>
+        <v>-2.6994</v>
       </c>
       <c r="E11" t="n">
-        <v>-4.4106</v>
+        <v>-1.6773</v>
       </c>
       <c r="F11" t="n">
-        <v>1.2231</v>
+        <v>-1.0221</v>
       </c>
       <c r="G11" t="n">
-        <v>-2.9174</v>
+        <v>-3.0893</v>
       </c>
       <c r="H11" t="n">
-        <v>-3.2051</v>
+        <v>-0.9981</v>
       </c>
       <c r="I11" t="n">
-        <v>0.2876</v>
+        <v>-2.0912</v>
       </c>
       <c r="J11" t="n">
-        <v>-2.6763</v>
+        <v>-0.432</v>
       </c>
       <c r="K11" t="n">
-        <v>-2.2772</v>
+        <v>1.6787</v>
       </c>
       <c r="L11" t="n">
-        <v>-0.3991</v>
+        <v>-2.1107</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.2412</v>
+        <v>-2.6573</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.9278</v>
+        <v>-2.6768</v>
       </c>
       <c r="O11" t="n">
-        <v>0.6867</v>
+        <v>0.0195</v>
       </c>
       <c r="P11" t="n">
-        <v>1.1903</v>
+        <v>-0.9919</v>
       </c>
       <c r="Q11" t="n">
-        <v>-1.9838</v>
+        <v>-2.9758</v>
       </c>
       <c r="R11" t="n">
-        <v>3.1741</v>
+        <v>1.9838</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.2539</v>
+        <v>-0.4279</v>
       </c>
       <c r="T11" t="n">
-        <v>0.2495</v>
+        <v>-0.0793</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.5034</v>
+        <v>-0.3486</v>
       </c>
       <c r="V11" t="n">
-        <v>-1.2065</v>
+        <v>1.8097</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>1.8097</v>
       </c>
       <c r="X11" t="n">
-        <v>-1.2065</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A. PILAN PERET</t>
+          <t>J. HAGENAERS COS</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,67 +1345,67 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-3.2067</v>
+        <v>-3.2566</v>
       </c>
       <c r="E12" t="n">
-        <v>-1.904</v>
+        <v>-4.592</v>
       </c>
       <c r="F12" t="n">
-        <v>-1.3027</v>
+        <v>1.3354</v>
       </c>
       <c r="G12" t="n">
-        <v>-3.0893</v>
+        <v>-2.9174</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.9981</v>
+        <v>-3.2051</v>
       </c>
       <c r="I12" t="n">
-        <v>-2.0912</v>
+        <v>0.2876</v>
       </c>
       <c r="J12" t="n">
-        <v>-0.432</v>
+        <v>-2.6763</v>
       </c>
       <c r="K12" t="n">
-        <v>1.6787</v>
+        <v>-2.2772</v>
       </c>
       <c r="L12" t="n">
-        <v>-2.1107</v>
+        <v>-0.3991</v>
       </c>
       <c r="M12" t="n">
-        <v>-2.6573</v>
+        <v>-0.2412</v>
       </c>
       <c r="N12" t="n">
-        <v>-2.6768</v>
+        <v>-0.9278</v>
       </c>
       <c r="O12" t="n">
-        <v>0.0195</v>
+        <v>0.6867</v>
       </c>
       <c r="P12" t="n">
-        <v>-0.9919</v>
+        <v>1.1903</v>
       </c>
       <c r="Q12" t="n">
-        <v>-2.9758</v>
+        <v>-1.9838</v>
       </c>
       <c r="R12" t="n">
-        <v>1.9838</v>
+        <v>3.1741</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.9352</v>
+        <v>-0.323</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.306</v>
+        <v>0.06809999999999999</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.6292</v>
+        <v>-0.3912</v>
       </c>
       <c r="V12" t="n">
-        <v>1.8097</v>
+        <v>-1.2065</v>
       </c>
       <c r="W12" t="n">
-        <v>1.8097</v>
+        <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>-1.2065</v>
       </c>
     </row>
     <row r="13">
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>10.6801</v>
+        <v>11.3037</v>
       </c>
       <c r="E13" t="n">
-        <v>9.7333</v>
+        <v>10.3568</v>
       </c>
       <c r="F13" t="n">
-        <v>0.9468000000000003</v>
+        <v>0.9465999999999997</v>
       </c>
       <c r="G13" t="n">
         <v>6.198</v>
@@ -1444,13 +1444,13 @@
         <v>14.6499</v>
       </c>
       <c r="K13" t="n">
-        <v>7.5902</v>
+        <v>7.590200000000003</v>
       </c>
       <c r="L13" t="n">
-        <v>7.0595</v>
+        <v>7.059500000000001</v>
       </c>
       <c r="M13" t="n">
-        <v>-8.452</v>
+        <v>-8.451999999999998</v>
       </c>
       <c r="N13" t="n">
         <v>-11.9501</v>
@@ -1468,10 +1468,10 @@
         <v>24.7981</v>
       </c>
       <c r="S13" t="n">
-        <v>-1.3884</v>
+        <v>-0.7648000000000001</v>
       </c>
       <c r="T13" t="n">
-        <v>1.2196</v>
+        <v>1.8431</v>
       </c>
       <c r="U13" t="n">
         <v>-2.608</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>9.703200000000001</v>
+        <v>9.3598</v>
       </c>
       <c r="E14" t="n">
-        <v>8.1098</v>
+        <v>8.415900000000001</v>
       </c>
       <c r="F14" t="n">
-        <v>1.5934</v>
+        <v>0.9439</v>
       </c>
       <c r="G14" t="n">
         <v>4.9728</v>
@@ -1546,13 +1546,13 @@
         <v>2.1822</v>
       </c>
       <c r="S14" t="n">
-        <v>1.3013</v>
+        <v>0.9578</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.1926</v>
+        <v>0.1135</v>
       </c>
       <c r="U14" t="n">
-        <v>1.4939</v>
+        <v>0.8444</v>
       </c>
       <c r="V14" t="n">
         <v>4.2226</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>2.4786</v>
+        <v>2.3341</v>
       </c>
       <c r="E15" t="n">
         <v>3.4117</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.9330000000000001</v>
+        <v>-1.0775</v>
       </c>
       <c r="G15" t="n">
         <v>0.758</v>
@@ -1624,13 +1624,13 @@
         <v>2.1822</v>
       </c>
       <c r="S15" t="n">
-        <v>1.1336</v>
+        <v>0.989</v>
       </c>
       <c r="T15" t="n">
         <v>0.5499000000000001</v>
       </c>
       <c r="U15" t="n">
-        <v>0.5837</v>
+        <v>0.4391</v>
       </c>
       <c r="V15" t="n">
         <v>-0.6032</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A. FERNANDEZ FUERTES</t>
+          <t>K. GUILLET</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,40 +1657,40 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.5546</v>
+        <v>-0.423</v>
       </c>
       <c r="E16" t="n">
-        <v>0.2026</v>
+        <v>0.9963</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.7572</v>
+        <v>-1.4192</v>
       </c>
       <c r="G16" t="n">
-        <v>-0.5696</v>
+        <v>-0.3026</v>
       </c>
       <c r="H16" t="n">
-        <v>2.2326</v>
+        <v>0.3476</v>
       </c>
       <c r="I16" t="n">
-        <v>-2.8023</v>
+        <v>-0.6502</v>
       </c>
       <c r="J16" t="n">
-        <v>1.1783</v>
+        <v>2.0469</v>
       </c>
       <c r="K16" t="n">
-        <v>3.2163</v>
+        <v>1.4017</v>
       </c>
       <c r="L16" t="n">
-        <v>-2.038</v>
+        <v>0.6451</v>
       </c>
       <c r="M16" t="n">
-        <v>-1.7479</v>
+        <v>-2.3495</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.9837</v>
+        <v>-1.0541</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.7642</v>
+        <v>-1.2954</v>
       </c>
       <c r="P16" t="n">
         <v>-1.9838</v>
@@ -1702,22 +1702,22 @@
         <v>1.9838</v>
       </c>
       <c r="S16" t="n">
-        <v>0.7924</v>
+        <v>-0.2835</v>
       </c>
       <c r="T16" t="n">
-        <v>1.7856</v>
+        <v>0.2381</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.9932</v>
+        <v>-0.5216</v>
       </c>
       <c r="V16" t="n">
-        <v>1.2065</v>
+        <v>2.1469</v>
       </c>
       <c r="W16" t="n">
-        <v>1.2065</v>
+        <v>2.6789</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>-0.532</v>
       </c>
     </row>
     <row r="17">
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.6182</v>
+        <v>-0.756</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.2714</v>
+        <v>-0.5775</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.3468</v>
+        <v>-0.1785</v>
       </c>
       <c r="G17" t="n">
         <v>-1.1613</v>
@@ -1780,13 +1780,13 @@
         <v>0.1984</v>
       </c>
       <c r="S17" t="n">
-        <v>0.3447</v>
+        <v>0.2069</v>
       </c>
       <c r="T17" t="n">
-        <v>0.3685</v>
+        <v>0.0624</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.0238</v>
+        <v>0.1445</v>
       </c>
       <c r="V17" t="n">
         <v>0</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>K. GUILLET</t>
+          <t>A. FERNANDEZ FUERTES</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,40 +1813,40 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.8413</v>
+        <v>-1.1685</v>
       </c>
       <c r="E18" t="n">
-        <v>0.6902</v>
+        <v>-0.7156</v>
       </c>
       <c r="F18" t="n">
-        <v>-1.5314</v>
+        <v>-0.4529</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.3026</v>
+        <v>-0.5696</v>
       </c>
       <c r="H18" t="n">
-        <v>0.3476</v>
+        <v>2.2326</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.6502</v>
+        <v>-2.8023</v>
       </c>
       <c r="J18" t="n">
-        <v>2.0469</v>
+        <v>1.1783</v>
       </c>
       <c r="K18" t="n">
-        <v>1.4017</v>
+        <v>3.2163</v>
       </c>
       <c r="L18" t="n">
-        <v>0.6451</v>
+        <v>-2.038</v>
       </c>
       <c r="M18" t="n">
-        <v>-2.3495</v>
+        <v>-1.7479</v>
       </c>
       <c r="N18" t="n">
-        <v>-1.0541</v>
+        <v>-0.9837</v>
       </c>
       <c r="O18" t="n">
-        <v>-1.2954</v>
+        <v>-0.7642</v>
       </c>
       <c r="P18" t="n">
         <v>-1.9838</v>
@@ -1858,28 +1858,28 @@
         <v>1.9838</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.7018</v>
+        <v>0.1785</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.0679</v>
+        <v>0.8673</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.6338</v>
+        <v>-0.6888</v>
       </c>
       <c r="V18" t="n">
-        <v>2.1469</v>
+        <v>1.2065</v>
       </c>
       <c r="W18" t="n">
-        <v>2.6789</v>
+        <v>1.2065</v>
       </c>
       <c r="X18" t="n">
-        <v>-0.532</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>J. MIRANDA VARGAS</t>
+          <t>X. ROSÀS MARCO</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.9639</v>
+        <v>-1.9844</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.4935</v>
+        <v>-3.2279</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.4704</v>
+        <v>1.2435</v>
       </c>
       <c r="G19" t="n">
-        <v>-1.4172</v>
+        <v>-4.6565</v>
       </c>
       <c r="H19" t="n">
-        <v>-1.9251</v>
+        <v>-0.1104</v>
       </c>
       <c r="I19" t="n">
-        <v>0.5079</v>
+        <v>-4.5462</v>
       </c>
       <c r="J19" t="n">
-        <v>0.4288</v>
+        <v>-3.4203</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.8564000000000001</v>
+        <v>0.6207</v>
       </c>
       <c r="L19" t="n">
-        <v>1.2852</v>
+        <v>-4.041</v>
       </c>
       <c r="M19" t="n">
-        <v>-1.846</v>
+        <v>-1.2363</v>
       </c>
       <c r="N19" t="n">
-        <v>-1.0688</v>
+        <v>-0.7311</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.7772</v>
+        <v>-0.5051</v>
       </c>
       <c r="P19" t="n">
-        <v>-2.1822</v>
+        <v>1.7855</v>
       </c>
       <c r="Q19" t="n">
-        <v>-2.9758</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>0.7935</v>
+        <v>1.7855</v>
       </c>
       <c r="S19" t="n">
-        <v>0.4291</v>
+        <v>0.6207</v>
       </c>
       <c r="T19" t="n">
-        <v>0.2438</v>
+        <v>-0.0736</v>
       </c>
       <c r="U19" t="n">
-        <v>0.1853</v>
+        <v>0.6943</v>
       </c>
       <c r="V19" t="n">
-        <v>1.2065</v>
+        <v>0.266</v>
       </c>
       <c r="W19" t="n">
-        <v>1.8097</v>
+        <v>0.266</v>
       </c>
       <c r="X19" t="n">
-        <v>-0.6032</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>X. ROSÀS MARCO</t>
+          <t>J. MIRANDA VARGAS</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,67 +1969,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-2.7649</v>
+        <v>-1.9919</v>
       </c>
       <c r="E20" t="n">
-        <v>-3.8401</v>
+        <v>-0.4935</v>
       </c>
       <c r="F20" t="n">
-        <v>1.0751</v>
+        <v>-1.4985</v>
       </c>
       <c r="G20" t="n">
-        <v>-4.6565</v>
+        <v>-1.4172</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.1104</v>
+        <v>-1.9251</v>
       </c>
       <c r="I20" t="n">
-        <v>-4.5462</v>
+        <v>0.5079</v>
       </c>
       <c r="J20" t="n">
-        <v>-3.4203</v>
+        <v>0.4288</v>
       </c>
       <c r="K20" t="n">
-        <v>0.6207</v>
+        <v>-0.8564000000000001</v>
       </c>
       <c r="L20" t="n">
-        <v>-4.041</v>
+        <v>1.2852</v>
       </c>
       <c r="M20" t="n">
-        <v>-1.2363</v>
+        <v>-1.846</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.7311</v>
+        <v>-1.0688</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.5051</v>
+        <v>-0.7772</v>
       </c>
       <c r="P20" t="n">
-        <v>1.7855</v>
+        <v>-2.1822</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>-2.9758</v>
       </c>
       <c r="R20" t="n">
-        <v>1.7855</v>
+        <v>0.7935</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.1599</v>
+        <v>0.401</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.6858</v>
+        <v>0.2438</v>
       </c>
       <c r="U20" t="n">
-        <v>0.5259</v>
+        <v>0.1572</v>
       </c>
       <c r="V20" t="n">
-        <v>0.266</v>
+        <v>1.2065</v>
       </c>
       <c r="W20" t="n">
-        <v>0.266</v>
+        <v>1.8097</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>-0.6032</v>
       </c>
     </row>
     <row r="21">
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-3.231</v>
+        <v>-2.7506</v>
       </c>
       <c r="E21" t="n">
-        <v>-2.3213</v>
+        <v>-2.1172</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.9097</v>
+        <v>-0.6334</v>
       </c>
       <c r="G21" t="n">
         <v>-1.2669</v>
@@ -2092,13 +2092,13 @@
         <v>0.1984</v>
       </c>
       <c r="S21" t="n">
-        <v>-1.1705</v>
+        <v>-0.6901</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.3117</v>
+        <v>-0.1077</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.8588</v>
+        <v>-0.5824</v>
       </c>
       <c r="V21" t="n">
         <v>0</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-4.5968</v>
+        <v>-5.561</v>
       </c>
       <c r="E22" t="n">
-        <v>0.2049</v>
+        <v>-0.8154</v>
       </c>
       <c r="F22" t="n">
-        <v>-4.8017</v>
+        <v>-4.7456</v>
       </c>
       <c r="G22" t="n">
         <v>-1.3367</v>
@@ -2170,13 +2170,13 @@
         <v>0.3968</v>
       </c>
       <c r="S22" t="n">
-        <v>0.7913</v>
+        <v>-0.1729</v>
       </c>
       <c r="T22" t="n">
-        <v>1.6665</v>
+        <v>0.6462</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.8752</v>
+        <v>-0.8191000000000001</v>
       </c>
       <c r="V22" t="n">
         <v>-1.4724</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-8.291399999999999</v>
+        <v>-7.0585</v>
       </c>
       <c r="E23" t="n">
-        <v>-6.6397</v>
+        <v>-5.8235</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.6516</v>
+        <v>-1.235</v>
       </c>
       <c r="G23" t="n">
         <v>-1.2179</v>
@@ -2248,13 +2248,13 @@
         <v>1.1903</v>
       </c>
       <c r="S23" t="n">
-        <v>-1.3717</v>
+        <v>-0.1389</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.7481</v>
+        <v>0.06809999999999999</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.6236</v>
+        <v>-0.207</v>
       </c>
       <c r="V23" t="n">
         <v>-0.9405</v>
@@ -2281,19 +2281,19 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-10.6803</v>
+        <v>-10</v>
       </c>
       <c r="E24" t="n">
-        <v>-0.9468000000000005</v>
+        <v>-0.9467000000000008</v>
       </c>
       <c r="F24" t="n">
-        <v>-9.733300000000002</v>
+        <v>-9.053199999999999</v>
       </c>
       <c r="G24" t="n">
         <v>-6.197900000000001</v>
       </c>
       <c r="H24" t="n">
-        <v>4.36</v>
+        <v>4.360000000000001</v>
       </c>
       <c r="I24" t="n">
         <v>-10.5581</v>
@@ -2305,7 +2305,7 @@
         <v>11.9503</v>
       </c>
       <c r="L24" t="n">
-        <v>-3.498400000000001</v>
+        <v>-3.498400000000002</v>
       </c>
       <c r="M24" t="n">
         <v>-14.6499</v>
@@ -2314,7 +2314,7 @@
         <v>-7.590199999999999</v>
       </c>
       <c r="O24" t="n">
-        <v>-7.059399999999999</v>
+        <v>-7.0594</v>
       </c>
       <c r="P24" t="n">
         <v>-11.9028</v>
@@ -2326,13 +2326,13 @@
         <v>12.8949</v>
       </c>
       <c r="S24" t="n">
-        <v>1.3885</v>
+        <v>2.0685</v>
       </c>
       <c r="T24" t="n">
-        <v>2.6082</v>
+        <v>2.608</v>
       </c>
       <c r="U24" t="n">
-        <v>-1.2196</v>
+        <v>-0.5393999999999999</v>
       </c>
       <c r="V24" t="n">
         <v>6.032399999999999</v>
